--- a/tame_output/ON/bt/strategyON_20240224.xlsx
+++ b/tame_output/ON/bt/strategyON_20240224.xlsx
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>1.490118930504397</v>
+        <v>1.490110576641966</v>
       </c>
       <c r="E1883" t="n">
-        <v>3.753635804871488</v>
+        <v>3.753632463326515</v>
       </c>
       <c r="F1883" t="n">
-        <v>2.433198655960514</v>
+        <v>2.433190302098082</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.617863850559785</v>
+        <v>4.617858838242326</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240224.xlsx
+++ b/tame_output/ON/bt/strategyON_20240224.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>448.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-10.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.5%</t>
+          <t>133.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.1%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
     </row>
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>1.490110576641966</v>
+        <v>1.509023442012804</v>
       </c>
       <c r="E1883" t="n">
-        <v>3.753632463326515</v>
+        <v>3.761197609474851</v>
       </c>
       <c r="F1883" t="n">
-        <v>2.433190302098082</v>
+        <v>2.452103167468921</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.617858838242326</v>
+        <v>4.62920655746483</v>
       </c>
     </row>
   </sheetData>
